--- a/1. DOCUMENTACION/TRIMESTRE II/Presupuesto Datastock.xlsx
+++ b/1. DOCUMENTACION/TRIMESTRE II/Presupuesto Datastock.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29914"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30007"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aprendiz\Desktop\DATASTOCK_DOCUMENTACION\1. DOCUMENTACION\TRIMESTRE II\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aprendiz\Documents\Nueva carpeta\DATASTOCK_DOCUMENTACION\1. DOCUMENTACION\TRIMESTRE II\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{29994AB5-2EFA-497D-B9D6-820D4720ADA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8131391C-A5A7-42E3-B0BC-06640627F544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EMPLEADOS" sheetId="1" r:id="rId1"/>
@@ -336,6 +336,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -346,12 +352,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -620,40 +620,40 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="D5" s="17" t="s">
+      <c r="B5" s="15"/>
+      <c r="D5" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="18"/>
-      <c r="I5" s="17" t="s">
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="22"/>
+      <c r="I5" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="18"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="22"/>
     </row>
     <row r="6" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="22"/>
-      <c r="B6" s="23"/>
-      <c r="D6" s="17" t="s">
+      <c r="A6" s="16"/>
+      <c r="B6" s="17"/>
+      <c r="D6" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="18"/>
+      <c r="E6" s="22"/>
       <c r="F6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="17" t="s">
+      <c r="I6" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="J6" s="18"/>
+      <c r="J6" s="22"/>
       <c r="K6" s="1" t="s">
         <v>7</v>
       </c>
@@ -675,13 +675,13 @@
         <f>B2*B7</f>
         <v>225250.00000000003</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="18">
         <f>B2+E7+E8+E9+E10+E11+E12+E13+E14+E15</f>
         <v>3966573</v>
       </c>
-      <c r="G7" s="14">
-        <f>F7/220</f>
-        <v>18029.877272727274</v>
+      <c r="G7" s="18">
+        <f>F7/160</f>
+        <v>24791.081249999999</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>9</v>
@@ -690,13 +690,13 @@
         <f>B3*B7</f>
         <v>272000</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="18">
         <f>B3+J7+J8+J9+J10+J11+J12+J13+J14+J15</f>
         <v>4786953</v>
       </c>
-      <c r="L7" s="14">
-        <f>K7/220</f>
-        <v>21758.877272727274</v>
+      <c r="L7" s="18">
+        <f>K7/160</f>
+        <v>29918.456249999999</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
@@ -713,8 +713,8 @@
         <f>B2*B8</f>
         <v>318000</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
       <c r="I8" s="1" t="s">
         <v>10</v>
       </c>
@@ -722,8 +722,8 @@
         <f>B3*B8</f>
         <v>384000</v>
       </c>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
     </row>
     <row r="9" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
@@ -739,8 +739,8 @@
         <f>B2*B9</f>
         <v>106000</v>
       </c>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
       <c r="I9" s="1" t="s">
         <v>11</v>
       </c>
@@ -748,8 +748,8 @@
         <f>B3*B9</f>
         <v>128000</v>
       </c>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
     </row>
     <row r="10" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
@@ -765,8 +765,8 @@
         <f>B2*B10</f>
         <v>13833</v>
       </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
       <c r="I10" s="1" t="s">
         <v>12</v>
       </c>
@@ -774,8 +774,8 @@
         <f t="shared" ref="J10:J11" si="0">B2*B10</f>
         <v>13833</v>
       </c>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
     </row>
     <row r="11" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
@@ -791,8 +791,8 @@
         <f>B2*B11</f>
         <v>220745</v>
       </c>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
       <c r="I11" s="1" t="s">
         <v>13</v>
       </c>
@@ -800,8 +800,8 @@
         <f t="shared" si="0"/>
         <v>266560</v>
       </c>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
     </row>
     <row r="12" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
@@ -817,8 +817,8 @@
         <f>B2*B12</f>
         <v>220745</v>
       </c>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
       <c r="I12" s="1" t="s">
         <v>14</v>
       </c>
@@ -826,8 +826,8 @@
         <f>B3*B12</f>
         <v>266560</v>
       </c>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
     </row>
     <row r="13" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
@@ -843,8 +843,8 @@
         <f>B2*B13</f>
         <v>26500</v>
       </c>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
       <c r="I13" s="1" t="s">
         <v>16</v>
       </c>
@@ -852,8 +852,8 @@
         <f>B3*B13</f>
         <v>32000</v>
       </c>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
     </row>
     <row r="14" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
@@ -869,8 +869,8 @@
         <f>B2*B14</f>
         <v>106000</v>
       </c>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
       <c r="I14" s="1" t="s">
         <v>17</v>
       </c>
@@ -878,8 +878,8 @@
         <f>B3*B14</f>
         <v>128000</v>
       </c>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
     </row>
     <row r="15" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
@@ -895,8 +895,8 @@
         <f>B2*B15</f>
         <v>79500</v>
       </c>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
       <c r="I15" s="1" t="s">
         <v>18</v>
       </c>
@@ -904,8 +904,8 @@
         <f>B3*B15</f>
         <v>96000</v>
       </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
@@ -954,15 +954,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="K7:K15"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="L7:L15"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="F7:F15"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="D5:G5"/>
     <mergeCell ref="G7:G15"/>
-    <mergeCell ref="K7:K15"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="L7:L15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -991,8 +991,8 @@
       <c r="A1" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="18"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="22"/>
       <c r="N1" s="8"/>
       <c r="O1" s="8"/>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="16"/>
+      <c r="A3" s="20"/>
       <c r="B3" s="10" t="s">
         <v>2</v>
       </c>
@@ -1041,7 +1041,7 @@
       </c>
     </row>
     <row r="6" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="15"/>
+      <c r="A6" s="19"/>
       <c r="B6" s="10" t="s">
         <v>25</v>
       </c>
@@ -1058,7 +1058,7 @@
       <c r="L6" s="8"/>
     </row>
     <row r="7" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="15"/>
+      <c r="A7" s="19"/>
       <c r="B7" s="10" t="s">
         <v>26</v>
       </c>
@@ -1075,7 +1075,7 @@
       <c r="L7" s="8"/>
     </row>
     <row r="8" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="15"/>
+      <c r="A8" s="19"/>
       <c r="B8" s="10" t="s">
         <v>27</v>
       </c>
@@ -1092,7 +1092,7 @@
       <c r="L8" s="4"/>
     </row>
     <row r="9" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="16"/>
+      <c r="A9" s="20"/>
       <c r="B9" s="10" t="s">
         <v>28</v>
       </c>
